--- a/data/saeop/건강생활지원.xlsx
+++ b/data/saeop/건강생활지원.xlsx
@@ -1246,7 +1246,7 @@
         <v>사진</v>
       </c>
       <c r="F24" t="str">
-        <v/>
+        <v>건강관리실</v>
       </c>
       <c r="G24" t="str">
         <v>건강관리실.jpg</v>
@@ -1278,7 +1278,7 @@
         <v>사진</v>
       </c>
       <c r="F25" t="str">
-        <v/>
+        <v>물리치료실</v>
       </c>
       <c r="G25" t="str">
         <v>물리치료실.jpg</v>
@@ -1310,7 +1310,7 @@
         <v>사진</v>
       </c>
       <c r="F26" t="str">
-        <v/>
+        <v>이미용서비스(여)</v>
       </c>
       <c r="G26" t="str">
         <v>KakaoTalk_20260902_160559380.jpg</v>
@@ -1342,7 +1342,7 @@
         <v>사진</v>
       </c>
       <c r="F27" t="str">
-        <v/>
+        <v>이미용서비스(남)</v>
       </c>
       <c r="G27" t="str">
         <v>KakaoTalk_20260917_111451227_02.jpg</v>

--- a/data/saeop/건강생활지원.xlsx
+++ b/data/saeop/건강생활지원.xlsx
@@ -769,7 +769,7 @@
         <v>문의</v>
       </c>
       <c r="G9" t="str">
-        <v>복지사업팀 033-747-0516</v>
+        <v>지역복지팀 033-747-0516</v>
       </c>
       <c r="H9" t="str">
         <v>phone</v>

--- a/data/saeop/건강생활지원.xlsx
+++ b/data/saeop/건강생활지원.xlsx
@@ -565,7 +565,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J37"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -1549,9 +1549,137 @@
         <v/>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>O</v>
+      </c>
+      <c r="B34" t="str">
+        <v>geongang</v>
+      </c>
+      <c r="C34" t="str">
+        <v/>
+      </c>
+      <c r="D34" t="str">
+        <v>기능회복지원</v>
+      </c>
+      <c r="E34" t="str">
+        <v>사진</v>
+      </c>
+      <c r="F34" t="str">
+        <v>치매예방인지활동(이론)</v>
+      </c>
+      <c r="G34" t="str">
+        <v>치매예방인지활동.jpg</v>
+      </c>
+      <c r="H34" t="str">
+        <v/>
+      </c>
+      <c r="I34" t="str">
+        <v/>
+      </c>
+      <c r="J34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>O</v>
+      </c>
+      <c r="B35" t="str">
+        <v>geongang</v>
+      </c>
+      <c r="C35" t="str">
+        <v/>
+      </c>
+      <c r="D35" t="str">
+        <v>기능회복지원</v>
+      </c>
+      <c r="E35" t="str">
+        <v>사진</v>
+      </c>
+      <c r="F35" t="str">
+        <v>치매예방인지활동(요리)</v>
+      </c>
+      <c r="G35" t="str">
+        <v>치매예방인지활동.jpg</v>
+      </c>
+      <c r="H35" t="str">
+        <v/>
+      </c>
+      <c r="I35" t="str">
+        <v/>
+      </c>
+      <c r="J35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>O</v>
+      </c>
+      <c r="B36" t="str">
+        <v>geongang</v>
+      </c>
+      <c r="C36" t="str">
+        <v/>
+      </c>
+      <c r="D36" t="str">
+        <v>기능회복지원</v>
+      </c>
+      <c r="E36" t="str">
+        <v>사진</v>
+      </c>
+      <c r="F36" t="str">
+        <v>치매예방인지활동(미술)</v>
+      </c>
+      <c r="G36" t="str">
+        <v>치매예방인지활동.jpg</v>
+      </c>
+      <c r="H36" t="str">
+        <v/>
+      </c>
+      <c r="I36" t="str">
+        <v/>
+      </c>
+      <c r="J36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>O</v>
+      </c>
+      <c r="B37" t="str">
+        <v>geongang</v>
+      </c>
+      <c r="C37" t="str">
+        <v/>
+      </c>
+      <c r="D37" t="str">
+        <v>기능회복지원</v>
+      </c>
+      <c r="E37" t="str">
+        <v>사진</v>
+      </c>
+      <c r="F37" t="str">
+        <v>치매예방인지활동(신체)</v>
+      </c>
+      <c r="G37" t="str">
+        <v>치매예방인지활동.jpg</v>
+      </c>
+      <c r="H37" t="str">
+        <v/>
+      </c>
+      <c r="I37" t="str">
+        <v/>
+      </c>
+      <c r="J37" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J33"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J37"/>
   </ignoredErrors>
 </worksheet>
 </file>